--- a/Amandos de ciacao de projecto.xlsx
+++ b/Amandos de ciacao de projecto.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="77">
   <si>
     <t>Passoa asseguir para a criacao de projecto</t>
   </si>
@@ -174,13 +174,128 @@
   </si>
   <si>
     <t>Observação</t>
+  </si>
+  <si>
+    <t>ls</t>
+  </si>
+  <si>
+    <t>Listar as pastas</t>
+  </si>
+  <si>
+    <t>cd ..</t>
+  </si>
+  <si>
+    <t>Voltar para pasta mediatamente anterior</t>
+  </si>
+  <si>
+    <t>code .</t>
+  </si>
+  <si>
+    <t>Abrir o vs code</t>
+  </si>
+  <si>
+    <t>dotnet --version</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verificar se o </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>dotnet</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> está instalado</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Instalar a ferramenta </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>dotnet-ef</t>
+    </r>
+  </si>
+  <si>
+    <t>dotnet tool install --global dotnet-ef</t>
+  </si>
+  <si>
+    <t>dotnet tool update --global dotnet-ef</t>
+  </si>
+  <si>
+    <t>Se já estiver instalada:</t>
+  </si>
+  <si>
+    <t>dotnet ef --version</t>
+  </si>
+  <si>
+    <t>Verificar:</t>
+  </si>
+  <si>
+    <t>dotnet ef migrations add InitialCreate</t>
+  </si>
+  <si>
+    <t>Criar uma Migration</t>
+  </si>
+  <si>
+    <t>Aplicar a Migration ao banco</t>
+  </si>
+  <si>
+    <t>dotnet ef database update</t>
+  </si>
+  <si>
+    <t>Listar as Migrations</t>
+  </si>
+  <si>
+    <t>dotnet ef migrations list</t>
+  </si>
+  <si>
+    <t>Remover a última Migration</t>
+  </si>
+  <si>
+    <t>dotnet ef migrations remove</t>
+  </si>
+  <si>
+    <t>dotnet ef migrations script</t>
+  </si>
+  <si>
+    <t>Gerar o script SQL</t>
+  </si>
+  <si>
+    <t>dotnet ef migrations script -o migration.sql</t>
+  </si>
+  <si>
+    <t>Para salvar em arquivo</t>
+  </si>
+  <si>
+    <t>Migration de banco de dados</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,6 +310,32 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -217,20 +358,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,247 +667,384 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="86.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="97.7109375" customWidth="1"/>
+    <col min="4" max="4" width="71.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+    </row>
+    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="5"/>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>37</v>
-      </c>
+    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
       <c r="B3" s="3"/>
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" t="s">
         <v>6</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C12" t="s">
         <v>8</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C13" t="s">
         <v>10</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="4" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C14" t="s">
         <v>12</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C15" t="s">
         <v>14</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C18" t="s">
         <v>16</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="4" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C19" t="s">
         <v>18</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="4" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C20" t="s">
         <v>20</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="4" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C21" t="s">
         <v>22</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D21" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C24" t="s">
         <v>24</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="4" t="s">
+    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C25" t="s">
         <v>26</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D25" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" t="s">
         <v>46</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C26" t="s">
         <v>28</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D26" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" t="s">
         <v>47</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C27" t="s">
         <v>30</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D27" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" t="s">
         <v>48</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C28" t="s">
         <v>32</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D28" t="s">
         <v>33</v>
       </c>
     </row>
+    <row r="31" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="A3:B6"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A31:B40"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="A7:B10"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Amandos de ciacao de projecto.xlsx
+++ b/Amandos de ciacao de projecto.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DVALOI\Desktop\AulasPraticas\APIDeslocacao\AulasPeog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Exercicio_Pretico\AulasPeog\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396E123D-FDEF-4152-A2A7-3638FE5E828B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4020"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +20,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -195,31 +199,6 @@
   </si>
   <si>
     <t>dotnet --version</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Verificar se o </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>dotnet</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="13.5"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> está instalado</t>
-    </r>
   </si>
   <si>
     <r>
@@ -290,12 +269,26 @@
   <si>
     <t>Migration de banco de dados</t>
   </si>
+  <si>
+    <r>
+      <t>Verificar se o dotnet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> está instalado</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,23 +312,29 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
       <sz val="13.5"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Courier New"/>
       <family val="3"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -358,34 +357,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -666,7 +662,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -677,18 +673,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="5"/>
+      <c r="B2" s="4"/>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
@@ -696,344 +692,349 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="1" t="s">
+    <row r="3" spans="1:4" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="7" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="1" t="s">
+    <row r="4" spans="1:4" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="1" t="s">
+    <row r="5" spans="1:4" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="6" spans="1:4" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+    </row>
+    <row r="7" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" t="s">
+    <row r="8" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" t="s">
+    <row r="9" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" t="s">
+    <row r="10" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="11" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8"/>
+      <c r="B13" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8"/>
+      <c r="B14" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8"/>
+      <c r="B15" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+    <row r="16" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="8"/>
+      <c r="B19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="8"/>
+      <c r="B20" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="8"/>
+      <c r="B21" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+    <row r="22" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="8"/>
+      <c r="B25" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" t="s">
+    <row r="26" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
+      <c r="B26" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" t="s">
+    <row r="27" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8"/>
+      <c r="B27" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" t="s">
+    <row r="28" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8"/>
+      <c r="B28" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31" s="8" t="s">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="7" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="7" t="s">
+      <c r="D33" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="9" t="s">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="7" t="s">
+      <c r="D34" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D34" s="9" t="s">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="7" t="s">
+      <c r="D35" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D35" s="8" t="s">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="5"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="7" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D36" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="7" t="s">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D37" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="7" t="s">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="7" t="s">
+      <c r="D39" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="8" t="s">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="7" t="s">
+      <c r="D40" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Amandos de ciacao de projecto.xlsx
+++ b/Amandos de ciacao de projecto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Exercicio_Pretico\AulasPeog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396E123D-FDEF-4152-A2A7-3638FE5E828B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC36C27-944C-495E-998A-E792FB05DBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -667,8 +667,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="86.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="123.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="71.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
